--- a/data/trans_dic/P13A_1_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_2023-Clase-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,96; 100,0</t>
+          <t>73,67; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,31; 100,0</t>
+          <t>81,21; 100,0</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,27; 99,58</t>
+          <t>87,61; 99,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,94; 99,69</t>
+          <t>90,07; 99,28</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -777,19 +777,19 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,59; 97,31</t>
+          <t>83,1; 97,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,42; 97,6</t>
+          <t>85,7; 97,84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>92,5; 98,23</t>
+          <t>91,83; 98,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93,74; 98,65</t>
+          <t>93,73; 98,36</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>16799</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10311; 13574</t>
+          <t>11048; 14996</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12127; 15291</t>
+          <t>14216; 17505</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13283</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>21554</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38034</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50773</t>
+          <t>56745</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35328; 38971</t>
+          <t>39729; 44932</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48730; 51716</t>
+          <t>52800; 58202</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>51506</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60702</t>
+          <t>63375</t>
         </is>
       </c>
     </row>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44485; 52412</t>
+          <t>46324; 54202</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55263; 63141</t>
+          <t>57945; 66155</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>21093</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>141532</t>
+          <t>152942</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178926</t>
+          <t>192850</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>136257; 144711</t>
+          <t>146706; 156686</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>173133; 182216</t>
+          <t>187143; 196405</t>
         </is>
       </c>
     </row>
